--- a/output/validation_report.xlsx
+++ b/output/validation_report.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Validation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
@@ -461,16 +461,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>257</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3"/>
@@ -533,121 +533,148 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+          <t>lof</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>List of Figures</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>avs, charging, contracts, epr, hub, negotiation, pps, spr, usb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lot</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>List of Tables</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>avs, charging, contracts, epr, hub, negotiation, pps, spr, usb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Tag Summary</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>avs</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>12</v>
-      </c>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>charging</t>
+          <t>avs</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>contracts</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>34</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>epr</t>
+          <t>contracts</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hub</t>
+          <t>epr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>hub</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>pps</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>spr</t>
+          <t>pps</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>spr</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>usb4</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>20</v>
+      <c r="B23" t="n">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/output/validation_report.xlsx
+++ b/output/validation_report.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
@@ -464,13 +464,13 @@
         <v>255</v>
       </c>
       <c r="C2" t="n">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3"/>
@@ -533,148 +533,121 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lof</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>List of Figures</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>avs, charging, contracts, epr, hub, negotiation, pps, spr, usb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>lot</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>List of Tables</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>avs, charging, contracts, epr, hub, negotiation, pps, spr, usb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tag Summary</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Tag Summary</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>avs</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>avs</t>
+          <t>charging</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>charging</t>
+          <t>contracts</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>257</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contracts</t>
+          <t>epr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>epr</t>
+          <t>hub</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hub</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>133</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>pps</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>pps</t>
+          <t>spr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>spr</t>
+          <t>usb4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>usb4</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
